--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260701.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260701.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,51 +616,51 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>14.12%</t>
+          <t>13.44%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>658,330,000</t>
+          <t>172,780,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>12.08%</t>
+          <t>12.07%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>172,780,000</t>
+          <t>658,330,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>11.87%</t>
+          <t>11.74%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>11.61%</t>
+          <t>11.62%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>7.05%</t>
+          <t>7.11%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.44%</t>
+          <t>4.19%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>4.12%</t>
         </is>
       </c>
     </row>
@@ -765,56 +765,56 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>38,395,000</t>
+          <t>37,585,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.83%</t>
+          <t>3.80%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>98,903,000</t>
+          <t>22,310,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.47%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>22,310,000</t>
+          <t>98,903,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.45%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>1,346</t>
+          <t>1,385</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>112,070,000</t>
+          <t>11,400,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,22 +887,22 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>11,400,000</t>
+          <t>112,070,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -924,51 +924,51 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>209,210,000</t>
+          <t>64,710,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>64,710,000</t>
+          <t>209,210,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>71,319,000</t>
+          <t>70,849,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.74%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
@@ -1078,73 +1078,73 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>12,198,000</t>
+          <t>119,100,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>119,100,000</t>
+          <t>8,444,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.65%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>8,444,000</t>
+          <t>12,198,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>26,819,000</t>
+          <t>14,250,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1320,46 +1320,46 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>38,623,000</t>
+          <t>26,819,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>14,250,000</t>
+          <t>41,370,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>41,370,000</t>
+          <t>38,623,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>長榮鋼</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>29,006,000</t>
+          <t>20,520,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>長榮鋼</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>20,520,000</t>
+          <t>29,006,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>2,554,569,430</t>
+          <t>3,802,991,470</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr"/>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>2,814,029,273</t>
+          <t>1,932,659,347</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr"/>
@@ -3159,20 +3159,38 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
+          <t>PFUR_NTD</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>PAYABLES FOR UNITS REDEEMED</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>-146,774,750</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
           <t>RDI_NTD</t>
         </is>
       </c>
-      <c r="B154" s="3" t="inlineStr">
+      <c r="B155" s="3" t="inlineStr">
         <is>
           <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
         </is>
       </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>-281,783,253</t>
-        </is>
-      </c>
-      <c r="D154" s="4" t="inlineStr"/>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>230,228,071</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
